--- a/data/2026-05-03/BallparkPal_Pitchers.xlsx
+++ b/data/2026-05-03/BallparkPal_Pitchers.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="129">
   <si>
     <t>GamePk</t>
   </si>
@@ -200,10 +200,10 @@
     <t xml:space="preserve">SD </t>
   </si>
   <si>
-    <t>Randy Vasquez</t>
-  </si>
-  <si>
-    <t>Vasquez</t>
+    <t>Griffin Canning</t>
+  </si>
+  <si>
+    <t>Canning</t>
   </si>
   <si>
     <t>Braxton Ashcraft</t>
@@ -224,6 +224,63 @@
     <t>Burns</t>
   </si>
   <si>
+    <t>Max Fried</t>
+  </si>
+  <si>
+    <t>Fried</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>Trey Gibson</t>
+  </si>
+  <si>
+    <t>Gibson</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>Joe Ryan</t>
+  </si>
+  <si>
+    <t>Ryan</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>Trey Yesavage</t>
+  </si>
+  <si>
+    <t>Yesavage</t>
+  </si>
+  <si>
+    <t>Chris Paddack</t>
+  </si>
+  <si>
+    <t>Paddack</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>Jesus Luzardo</t>
+  </si>
+  <si>
+    <t>Luzardo</t>
+  </si>
+  <si>
     <t>4:07</t>
   </si>
   <si>
@@ -245,6 +302,27 @@
     <t>Kochanowicz</t>
   </si>
   <si>
+    <t>7:20</t>
+  </si>
+  <si>
+    <t>Tyler Holton</t>
+  </si>
+  <si>
+    <t>Holton</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>Jack Leiter</t>
+  </si>
+  <si>
+    <t>Leiter</t>
+  </si>
+  <si>
     <t>3:10</t>
   </si>
   <si>
@@ -285,6 +363,24 @@
   </si>
   <si>
     <t>Boyd</t>
+  </si>
+  <si>
+    <t>Ranger Suarez</t>
+  </si>
+  <si>
+    <t>Suarez</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>Cody Bolton</t>
+  </si>
+  <si>
+    <t>Bolton</t>
   </si>
   <si>
     <t>4:05</t>
@@ -645,7 +741,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -754,46 +850,46 @@
         <v>31</v>
       </c>
       <c r="K2">
-        <v>21.822</v>
+        <v>22.251</v>
       </c>
       <c r="L2">
-        <v>4.921</v>
+        <v>4.999</v>
       </c>
       <c r="M2">
-        <v>0.173</v>
+        <v>0.189</v>
       </c>
       <c r="N2">
-        <v>0.399</v>
+        <v>0.398</v>
       </c>
       <c r="O2">
-        <v>0.429</v>
+        <v>0.413</v>
       </c>
       <c r="P2">
-        <v>0.235</v>
+        <v>0.245</v>
       </c>
       <c r="Q2">
-        <v>7.865</v>
+        <v>7.689</v>
       </c>
       <c r="R2">
-        <v>17.501</v>
+        <v>17.446</v>
       </c>
       <c r="S2">
-        <v>2.765</v>
+        <v>2.882</v>
       </c>
       <c r="T2">
-        <v>5.407</v>
+        <v>5.649</v>
       </c>
       <c r="U2">
-        <v>3.02</v>
+        <v>2.994</v>
       </c>
       <c r="V2">
-        <v>1.936</v>
+        <v>1.924</v>
       </c>
       <c r="W2">
-        <v>0.69</v>
+        <v>0.767</v>
       </c>
       <c r="X2">
-        <v>1.005</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -828,46 +924,46 @@
         <v>30</v>
       </c>
       <c r="K3">
-        <v>18.86</v>
+        <v>18.845</v>
       </c>
       <c r="L3">
-        <v>4.377</v>
+        <v>4.358</v>
       </c>
       <c r="M3">
-        <v>0.132</v>
+        <v>0.127</v>
       </c>
       <c r="N3">
-        <v>0.184</v>
+        <v>0.203</v>
       </c>
       <c r="O3">
-        <v>0.683</v>
+        <v>0.67</v>
       </c>
       <c r="P3">
-        <v>0.084</v>
+        <v>0.074</v>
       </c>
       <c r="Q3">
-        <v>10.408</v>
+        <v>10.219</v>
       </c>
       <c r="R3">
-        <v>19.645</v>
+        <v>19.387</v>
       </c>
       <c r="S3">
-        <v>1.941</v>
+        <v>1.968</v>
       </c>
       <c r="T3">
-        <v>4.185</v>
+        <v>4.241</v>
       </c>
       <c r="U3">
-        <v>3.735</v>
+        <v>3.721</v>
       </c>
       <c r="V3">
-        <v>1.747</v>
+        <v>1.757</v>
       </c>
       <c r="W3">
-        <v>0.365</v>
+        <v>0.404</v>
       </c>
       <c r="X3">
-        <v>0.592</v>
+        <v>0.565</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -902,46 +998,46 @@
         <v>40</v>
       </c>
       <c r="K4">
-        <v>19.729</v>
+        <v>19.891</v>
       </c>
       <c r="L4">
-        <v>4.684</v>
+        <v>4.745</v>
       </c>
       <c r="M4">
-        <v>0.221</v>
+        <v>0.252</v>
       </c>
       <c r="N4">
-        <v>0.249</v>
+        <v>0.238</v>
       </c>
       <c r="O4">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="P4">
-        <v>0.15</v>
+        <v>0.162</v>
       </c>
       <c r="Q4">
-        <v>11.319</v>
+        <v>11.814</v>
       </c>
       <c r="R4">
-        <v>21.073</v>
+        <v>21.764</v>
       </c>
       <c r="S4">
-        <v>2.089</v>
+        <v>2.032</v>
       </c>
       <c r="T4">
-        <v>4.726</v>
+        <v>4.64</v>
       </c>
       <c r="U4">
-        <v>3.787</v>
+        <v>3.823</v>
       </c>
       <c r="V4">
-        <v>1.107</v>
+        <v>1.123</v>
       </c>
       <c r="W4">
-        <v>0.589</v>
+        <v>0.58</v>
       </c>
       <c r="X4">
-        <v>0.213</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -976,46 +1072,46 @@
         <v>39</v>
       </c>
       <c r="K5">
-        <v>21.665</v>
+        <v>21.929</v>
       </c>
       <c r="L5">
-        <v>4.908</v>
+        <v>4.945</v>
       </c>
       <c r="M5">
-        <v>0.159</v>
+        <v>0.164</v>
       </c>
       <c r="N5">
-        <v>0.346</v>
+        <v>0.374</v>
       </c>
       <c r="O5">
-        <v>0.495</v>
+        <v>0.462</v>
       </c>
       <c r="P5">
-        <v>0.225</v>
+        <v>0.239</v>
       </c>
       <c r="Q5">
-        <v>10.38</v>
+        <v>9.963</v>
       </c>
       <c r="R5">
-        <v>21.007</v>
+        <v>20.646</v>
       </c>
       <c r="S5">
-        <v>2.616</v>
+        <v>2.687</v>
       </c>
       <c r="T5">
-        <v>5.044</v>
+        <v>5.12</v>
       </c>
       <c r="U5">
-        <v>4.092</v>
+        <v>3.979</v>
       </c>
       <c r="V5">
-        <v>2.051</v>
+        <v>2.215</v>
       </c>
       <c r="W5">
-        <v>0.661</v>
+        <v>0.653</v>
       </c>
       <c r="X5">
-        <v>0.549</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1050,46 +1146,46 @@
         <v>47</v>
       </c>
       <c r="K6">
-        <v>22.769</v>
+        <v>23.234</v>
       </c>
       <c r="L6">
-        <v>5.225</v>
+        <v>5.307</v>
       </c>
       <c r="M6">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="N6">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="O6">
-        <v>0.393</v>
+        <v>0.387</v>
       </c>
       <c r="P6">
-        <v>0.316</v>
+        <v>0.324</v>
       </c>
       <c r="Q6">
-        <v>10.702</v>
+        <v>10.708</v>
       </c>
       <c r="R6">
-        <v>21.982</v>
+        <v>22.206</v>
       </c>
       <c r="S6">
-        <v>2.651</v>
+        <v>2.817</v>
       </c>
       <c r="T6">
-        <v>4.975</v>
+        <v>5.247</v>
       </c>
       <c r="U6">
-        <v>3.929</v>
+        <v>4.077</v>
       </c>
       <c r="V6">
-        <v>2.405</v>
+        <v>2.369</v>
       </c>
       <c r="W6">
-        <v>0.752</v>
+        <v>0.823</v>
       </c>
       <c r="X6">
-        <v>0.64</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1124,46 +1220,46 @@
         <v>46</v>
       </c>
       <c r="K7">
-        <v>18.846</v>
+        <v>18.848</v>
       </c>
       <c r="L7">
-        <v>4.466</v>
+        <v>4.411</v>
       </c>
       <c r="M7">
-        <v>0.135</v>
+        <v>0.144</v>
       </c>
       <c r="N7">
-        <v>0.203</v>
+        <v>0.199</v>
       </c>
       <c r="O7">
-        <v>0.662</v>
+        <v>0.657</v>
       </c>
       <c r="P7">
-        <v>0.102</v>
+        <v>0.085</v>
       </c>
       <c r="Q7">
-        <v>10.29</v>
+        <v>9.979</v>
       </c>
       <c r="R7">
-        <v>19.188</v>
+        <v>18.852</v>
       </c>
       <c r="S7">
-        <v>1.837</v>
+        <v>1.955</v>
       </c>
       <c r="T7">
-        <v>4.279</v>
+        <v>4.44</v>
       </c>
       <c r="U7">
-        <v>3.361</v>
+        <v>3.427</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.333</v>
       </c>
       <c r="W7">
-        <v>0.45</v>
+        <v>0.485</v>
       </c>
       <c r="X7">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1198,46 +1294,46 @@
         <v>54</v>
       </c>
       <c r="K8">
-        <v>22.732</v>
+        <v>22.664</v>
       </c>
       <c r="L8">
-        <v>5.437</v>
+        <v>5.355</v>
       </c>
       <c r="M8">
-        <v>0.283</v>
+        <v>0.265</v>
       </c>
       <c r="N8">
-        <v>0.322</v>
+        <v>0.326</v>
       </c>
       <c r="O8">
-        <v>0.395</v>
+        <v>0.41</v>
       </c>
       <c r="P8">
-        <v>0.387</v>
+        <v>0.362</v>
       </c>
       <c r="Q8">
-        <v>13.508</v>
+        <v>12.96</v>
       </c>
       <c r="R8">
-        <v>25.691</v>
+        <v>24.995</v>
       </c>
       <c r="S8">
-        <v>2.222</v>
+        <v>2.366</v>
       </c>
       <c r="T8">
-        <v>4.914</v>
+        <v>5.018</v>
       </c>
       <c r="U8">
-        <v>4.267</v>
+        <v>4.33</v>
       </c>
       <c r="V8">
-        <v>1.686</v>
+        <v>1.792</v>
       </c>
       <c r="W8">
-        <v>0.653</v>
+        <v>0.721</v>
       </c>
       <c r="X8">
-        <v>0.575</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1272,46 +1368,46 @@
         <v>53</v>
       </c>
       <c r="K9">
-        <v>21.566</v>
+        <v>21.883</v>
       </c>
       <c r="L9">
-        <v>5.079</v>
+        <v>5.14</v>
       </c>
       <c r="M9">
-        <v>0.187</v>
+        <v>0.183</v>
       </c>
       <c r="N9">
-        <v>0.316</v>
+        <v>0.308</v>
       </c>
       <c r="O9">
-        <v>0.497</v>
+        <v>0.509</v>
       </c>
       <c r="P9">
-        <v>0.293</v>
+        <v>0.314</v>
       </c>
       <c r="Q9">
-        <v>14.365</v>
+        <v>14.533</v>
       </c>
       <c r="R9">
-        <v>26.655</v>
+        <v>27.096</v>
       </c>
       <c r="S9">
-        <v>2.134</v>
+        <v>2.207</v>
       </c>
       <c r="T9">
-        <v>3.816</v>
+        <v>3.963</v>
       </c>
       <c r="U9">
-        <v>5.175</v>
+        <v>5.315</v>
       </c>
       <c r="V9">
-        <v>2.679</v>
+        <v>2.684</v>
       </c>
       <c r="W9">
-        <v>0.712</v>
+        <v>0.729</v>
       </c>
       <c r="X9">
-        <v>0.339</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1346,46 +1442,46 @@
         <v>60</v>
       </c>
       <c r="K10">
-        <v>18.359</v>
+        <v>18.441</v>
       </c>
       <c r="L10">
-        <v>3.967</v>
+        <v>3.973</v>
       </c>
       <c r="M10">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="N10">
-        <v>0.464</v>
+        <v>0.458</v>
       </c>
       <c r="O10">
-        <v>0.481</v>
+        <v>0.484</v>
       </c>
       <c r="P10">
         <v>0.037</v>
       </c>
       <c r="Q10">
-        <v>5.129</v>
+        <v>5.184</v>
       </c>
       <c r="R10">
-        <v>12.361</v>
+        <v>12.515</v>
       </c>
       <c r="S10">
-        <v>2.685</v>
+        <v>2.663</v>
       </c>
       <c r="T10">
-        <v>4.445</v>
+        <v>4.434</v>
       </c>
       <c r="U10">
-        <v>2.678</v>
+        <v>2.696</v>
       </c>
       <c r="V10">
-        <v>2.232</v>
+        <v>2.323</v>
       </c>
       <c r="W10">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="X10">
-        <v>0.338</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1399,7 +1495,7 @@
         <v>50</v>
       </c>
       <c r="D11">
-        <v>681190</v>
+        <v>656288</v>
       </c>
       <c r="E11" t="s">
         <v>61</v>
@@ -1420,46 +1516,46 @@
         <v>59</v>
       </c>
       <c r="K11">
-        <v>23.152</v>
+        <v>20.49</v>
       </c>
       <c r="L11">
-        <v>5.588</v>
+        <v>4.89</v>
       </c>
       <c r="M11">
-        <v>0.439</v>
+        <v>0.345</v>
       </c>
       <c r="N11">
-        <v>0.176</v>
+        <v>0.159</v>
       </c>
       <c r="O11">
-        <v>0.385</v>
+        <v>0.495</v>
       </c>
       <c r="P11">
-        <v>0.434</v>
+        <v>0.219</v>
       </c>
       <c r="Q11">
-        <v>18.295</v>
+        <v>14.561</v>
       </c>
       <c r="R11">
-        <v>32.872</v>
+        <v>26.298</v>
       </c>
       <c r="S11">
-        <v>1.955</v>
+        <v>1.83</v>
       </c>
       <c r="T11">
-        <v>4.291</v>
+        <v>3.762</v>
       </c>
       <c r="U11">
-        <v>5.868</v>
+        <v>4.723</v>
       </c>
       <c r="V11">
-        <v>2.179</v>
+        <v>2.255</v>
       </c>
       <c r="W11">
-        <v>0.578</v>
+        <v>0.537</v>
       </c>
       <c r="X11">
-        <v>0.313</v>
+        <v>0.256</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1494,46 +1590,46 @@
         <v>66</v>
       </c>
       <c r="K12">
-        <v>22.916</v>
+        <v>23.678</v>
       </c>
       <c r="L12">
-        <v>5.597</v>
+        <v>5.782</v>
       </c>
       <c r="M12">
-        <v>0.293</v>
+        <v>0.326</v>
       </c>
       <c r="N12">
-        <v>0.275</v>
+        <v>0.259</v>
       </c>
       <c r="O12">
-        <v>0.432</v>
+        <v>0.414</v>
       </c>
       <c r="P12">
-        <v>0.439</v>
+        <v>0.484</v>
       </c>
       <c r="Q12">
-        <v>19.224</v>
+        <v>19.576</v>
       </c>
       <c r="R12">
-        <v>34.091</v>
+        <v>34.914</v>
       </c>
       <c r="S12">
-        <v>1.679</v>
+        <v>1.771</v>
       </c>
       <c r="T12">
-        <v>3.834</v>
+        <v>4.04</v>
       </c>
       <c r="U12">
-        <v>6.274</v>
+        <v>6.329</v>
       </c>
       <c r="V12">
-        <v>2.439</v>
+        <v>2.468</v>
       </c>
       <c r="W12">
-        <v>0.385</v>
+        <v>0.392</v>
       </c>
       <c r="X12">
-        <v>0.663</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1568,288 +1664,288 @@
         <v>65</v>
       </c>
       <c r="K13">
-        <v>18.687</v>
+        <v>18.818</v>
       </c>
       <c r="L13">
-        <v>4.533</v>
+        <v>4.487</v>
       </c>
       <c r="M13">
-        <v>0.125</v>
+        <v>0.114</v>
       </c>
       <c r="N13">
-        <v>0.281</v>
+        <v>0.307</v>
       </c>
       <c r="O13">
-        <v>0.594</v>
+        <v>0.579</v>
       </c>
       <c r="P13">
-        <v>0.106</v>
+        <v>0.098</v>
       </c>
       <c r="Q13">
-        <v>15.098</v>
+        <v>14.402</v>
       </c>
       <c r="R13">
-        <v>26.044</v>
+        <v>25.207</v>
       </c>
       <c r="S13">
-        <v>1.492</v>
+        <v>1.607</v>
       </c>
       <c r="T13">
-        <v>3.196</v>
+        <v>3.336</v>
       </c>
       <c r="U13">
-        <v>5.25</v>
+        <v>5.163</v>
       </c>
       <c r="V13">
-        <v>1.999</v>
+        <v>2.105</v>
       </c>
       <c r="W13">
-        <v>0.449</v>
+        <v>0.439</v>
       </c>
       <c r="X13">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
     </row>
     <row r="14" spans="1:24">
       <c r="A14">
-        <v>824043</v>
+        <v>823555</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
       <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>608331</v>
+      </c>
+      <c r="E14" t="s">
         <v>69</v>
       </c>
-      <c r="D14">
-        <v>605280</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>70</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
         <v>71</v>
       </c>
-      <c r="G14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>72</v>
       </c>
-      <c r="J14" t="s">
-        <v>73</v>
-      </c>
       <c r="K14">
-        <v>21.387</v>
+        <v>25.556</v>
       </c>
       <c r="L14">
-        <v>4.877</v>
+        <v>6.138</v>
       </c>
       <c r="M14">
-        <v>0.186</v>
+        <v>0.434</v>
       </c>
       <c r="N14">
-        <v>0.23</v>
+        <v>0.225</v>
       </c>
       <c r="O14">
-        <v>0.584</v>
+        <v>0.34</v>
       </c>
       <c r="P14">
-        <v>0.237</v>
+        <v>0.568</v>
       </c>
       <c r="Q14">
-        <v>10.151</v>
+        <v>17.219</v>
       </c>
       <c r="R14">
-        <v>20.785</v>
+        <v>32.366</v>
       </c>
       <c r="S14">
-        <v>2.539</v>
+        <v>2.257</v>
       </c>
       <c r="T14">
-        <v>4.931</v>
+        <v>4.896</v>
       </c>
       <c r="U14">
-        <v>3.903</v>
+        <v>5.282</v>
       </c>
       <c r="V14">
-        <v>2.234</v>
+        <v>2.504</v>
       </c>
       <c r="W14">
-        <v>0.615</v>
+        <v>0.602</v>
       </c>
       <c r="X14">
-        <v>0.405</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="15" spans="1:24">
       <c r="A15">
-        <v>824043</v>
+        <v>823555</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="D15">
-        <v>686799</v>
+        <v>694346</v>
       </c>
       <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s">
         <v>74</v>
-      </c>
-      <c r="F15" t="s">
-        <v>75</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K15">
-        <v>23.06</v>
+        <v>18.478</v>
       </c>
       <c r="L15">
-        <v>5.072</v>
+        <v>4.05</v>
       </c>
       <c r="M15">
-        <v>0.203</v>
+        <v>0.068</v>
       </c>
       <c r="N15">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="O15">
-        <v>0.403</v>
+        <v>0.542</v>
       </c>
       <c r="P15">
-        <v>0.262</v>
+        <v>0.044</v>
       </c>
       <c r="Q15">
-        <v>7.289</v>
+        <v>8.305</v>
       </c>
       <c r="R15">
-        <v>17.571</v>
+        <v>16.958</v>
       </c>
       <c r="S15">
-        <v>3.241</v>
+        <v>2.365</v>
       </c>
       <c r="T15">
-        <v>6.071</v>
+        <v>4.054</v>
       </c>
       <c r="U15">
-        <v>3.271</v>
+        <v>3.774</v>
       </c>
       <c r="V15">
-        <v>2.264</v>
+        <v>2.44</v>
       </c>
       <c r="W15">
-        <v>0.693</v>
+        <v>0.606</v>
       </c>
       <c r="X15">
-        <v>0.447</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="16" spans="1:24">
       <c r="A16">
-        <v>824364</v>
+        <v>823711</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
       <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16">
+        <v>657746</v>
+      </c>
+      <c r="E16" t="s">
         <v>76</v>
       </c>
-      <c r="D16">
-        <v>607536</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>77</v>
       </c>
-      <c r="F16" t="s">
-        <v>78</v>
-      </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H16" t="s">
         <v>29</v>
       </c>
       <c r="I16" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" t="s">
         <v>79</v>
       </c>
-      <c r="J16" t="s">
-        <v>80</v>
-      </c>
       <c r="K16">
-        <v>22.823</v>
+        <v>24.192</v>
       </c>
       <c r="L16">
-        <v>5.175</v>
+        <v>5.886</v>
       </c>
       <c r="M16">
-        <v>0.302</v>
+        <v>0.289</v>
       </c>
       <c r="N16">
-        <v>0.287</v>
+        <v>0.311</v>
       </c>
       <c r="O16">
-        <v>0.411</v>
+        <v>0.4</v>
       </c>
       <c r="P16">
-        <v>0.284</v>
+        <v>0.483</v>
       </c>
       <c r="Q16">
-        <v>8.522</v>
+        <v>16.584</v>
       </c>
       <c r="R16">
-        <v>18.772</v>
+        <v>30.499</v>
       </c>
       <c r="S16">
-        <v>3.112</v>
+        <v>2.36</v>
       </c>
       <c r="T16">
-        <v>6.28</v>
+        <v>5.208</v>
       </c>
       <c r="U16">
-        <v>3.211</v>
+        <v>5.419</v>
       </c>
       <c r="V16">
-        <v>1.278</v>
+        <v>1.394</v>
       </c>
       <c r="W16">
-        <v>0.802</v>
+        <v>0.82</v>
       </c>
       <c r="X16">
-        <v>0.47</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="17" spans="1:24">
       <c r="A17">
-        <v>824364</v>
+        <v>823711</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17">
-        <v>675911</v>
+        <v>702056</v>
       </c>
       <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" t="s">
         <v>81</v>
-      </c>
-      <c r="F17" t="s">
-        <v>82</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1858,348 +1954,1088 @@
         <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K17">
-        <v>19.751</v>
+        <v>21.482</v>
       </c>
       <c r="L17">
-        <v>4.233</v>
+        <v>5.004</v>
       </c>
       <c r="M17">
-        <v>0.119</v>
+        <v>0.17</v>
       </c>
       <c r="N17">
-        <v>0.338</v>
+        <v>0.288</v>
       </c>
       <c r="O17">
-        <v>0.543</v>
+        <v>0.542</v>
       </c>
       <c r="P17">
-        <v>0.085</v>
+        <v>0.283</v>
       </c>
       <c r="Q17">
-        <v>5.362</v>
+        <v>15.353</v>
       </c>
       <c r="R17">
-        <v>13.332</v>
+        <v>28.185</v>
       </c>
       <c r="S17">
-        <v>3.304</v>
+        <v>2.135</v>
       </c>
       <c r="T17">
-        <v>5.483</v>
+        <v>4.17</v>
       </c>
       <c r="U17">
-        <v>3.163</v>
+        <v>5.807</v>
       </c>
       <c r="V17">
-        <v>1.78</v>
+        <v>2.387</v>
       </c>
       <c r="W17">
-        <v>0.939</v>
+        <v>0.61</v>
       </c>
       <c r="X17">
-        <v>0.445</v>
+        <v>0.359</v>
       </c>
     </row>
     <row r="18" spans="1:24">
       <c r="A18">
-        <v>824687</v>
+        <v>823875</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
       <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18">
+        <v>663978</v>
+      </c>
+      <c r="E18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" t="s">
         <v>83</v>
-      </c>
-      <c r="D18">
-        <v>518876</v>
-      </c>
-      <c r="E18" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" t="s">
-        <v>85</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K18">
-        <v>21.821</v>
+        <v>22.733</v>
       </c>
       <c r="L18">
-        <v>4.66</v>
+        <v>5.423</v>
       </c>
       <c r="M18">
-        <v>0.128</v>
+        <v>0.221</v>
       </c>
       <c r="N18">
         <v>0.394</v>
       </c>
       <c r="O18">
-        <v>0.478</v>
+        <v>0.386</v>
       </c>
       <c r="P18">
-        <v>0.176</v>
+        <v>0.365</v>
       </c>
       <c r="Q18">
-        <v>5.048</v>
+        <v>12.865</v>
       </c>
       <c r="R18">
-        <v>13.866</v>
+        <v>24.653</v>
       </c>
       <c r="S18">
-        <v>3.489</v>
+        <v>2.346</v>
       </c>
       <c r="T18">
-        <v>5.86</v>
+        <v>5.121</v>
       </c>
       <c r="U18">
-        <v>2.961</v>
+        <v>4.213</v>
       </c>
       <c r="V18">
-        <v>2.294</v>
+        <v>1.515</v>
       </c>
       <c r="W18">
-        <v>0.969</v>
+        <v>0.658</v>
       </c>
       <c r="X18">
-        <v>0.519</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="19" spans="1:24">
       <c r="A19">
-        <v>824687</v>
+        <v>823875</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="D19">
-        <v>571510</v>
+        <v>666200</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s">
         <v>38</v>
       </c>
       <c r="H19" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K19">
-        <v>21.776</v>
+        <v>23.746</v>
       </c>
       <c r="L19">
-        <v>4.921</v>
+        <v>5.815</v>
       </c>
       <c r="M19">
-        <v>0.295</v>
+        <v>0.269</v>
       </c>
       <c r="N19">
-        <v>0.237</v>
+        <v>0.248</v>
       </c>
       <c r="O19">
-        <v>0.468</v>
+        <v>0.483</v>
       </c>
       <c r="P19">
-        <v>0.235</v>
+        <v>0.521</v>
       </c>
       <c r="Q19">
-        <v>11.067</v>
+        <v>18.805</v>
       </c>
       <c r="R19">
-        <v>22.168</v>
+        <v>33.902</v>
       </c>
       <c r="S19">
-        <v>2.749</v>
+        <v>2.053</v>
       </c>
       <c r="T19">
-        <v>5.476</v>
+        <v>5.021</v>
       </c>
       <c r="U19">
-        <v>4.315</v>
+        <v>6.307</v>
       </c>
       <c r="V19">
-        <v>1.719</v>
+        <v>1.472</v>
       </c>
       <c r="W19">
-        <v>0.766</v>
+        <v>0.469</v>
       </c>
       <c r="X19">
-        <v>0.36</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="20" spans="1:24">
       <c r="A20">
-        <v>825013</v>
+        <v>824043</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
       </c>
       <c r="C20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20">
+        <v>605280</v>
+      </c>
+      <c r="E20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" t="s">
         <v>90</v>
-      </c>
-      <c r="D20">
-        <v>650644</v>
-      </c>
-      <c r="E20" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" t="s">
-        <v>92</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
       </c>
       <c r="H20" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K20">
-        <v>21.997</v>
+        <v>22.229</v>
       </c>
       <c r="L20">
-        <v>5.195</v>
+        <v>5.113</v>
       </c>
       <c r="M20">
-        <v>0.214</v>
+        <v>0.209</v>
       </c>
       <c r="N20">
-        <v>0.365</v>
+        <v>0.244</v>
       </c>
       <c r="O20">
-        <v>0.421</v>
+        <v>0.547</v>
       </c>
       <c r="P20">
-        <v>0.293</v>
+        <v>0.278</v>
       </c>
       <c r="Q20">
-        <v>11.007</v>
+        <v>10.852</v>
       </c>
       <c r="R20">
-        <v>21.598</v>
+        <v>22.055</v>
       </c>
       <c r="S20">
-        <v>2.508</v>
+        <v>2.627</v>
       </c>
       <c r="T20">
-        <v>5.215</v>
+        <v>5.021</v>
       </c>
       <c r="U20">
-        <v>3.695</v>
+        <v>4.077</v>
       </c>
       <c r="V20">
-        <v>1.318</v>
+        <v>2.297</v>
       </c>
       <c r="W20">
-        <v>0.841</v>
+        <v>0.67</v>
       </c>
       <c r="X20">
-        <v>0.384</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="21" spans="1:24">
       <c r="A21">
-        <v>825013</v>
+        <v>824043</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D21">
+        <v>686799</v>
+      </c>
+      <c r="E21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" t="s">
+        <v>92</v>
+      </c>
+      <c r="J21" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21">
+        <v>23.742</v>
+      </c>
+      <c r="L21">
+        <v>5.259</v>
+      </c>
+      <c r="M21">
+        <v>0.223</v>
+      </c>
+      <c r="N21">
+        <v>0.392</v>
+      </c>
+      <c r="O21">
+        <v>0.385</v>
+      </c>
+      <c r="P21">
+        <v>0.298</v>
+      </c>
+      <c r="Q21">
+        <v>7.853</v>
+      </c>
+      <c r="R21">
+        <v>18.625</v>
+      </c>
+      <c r="S21">
+        <v>3.245</v>
+      </c>
+      <c r="T21">
+        <v>6.049</v>
+      </c>
+      <c r="U21">
+        <v>3.351</v>
+      </c>
+      <c r="V21">
+        <v>2.441</v>
+      </c>
+      <c r="W21">
+        <v>0.738</v>
+      </c>
+      <c r="X21">
+        <v>0.382</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
+      <c r="A22">
+        <v>824285</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22">
+        <v>663947</v>
+      </c>
+      <c r="E22" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>98</v>
+      </c>
+      <c r="J22" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22">
+        <v>6.947</v>
+      </c>
+      <c r="L22">
+        <v>1.549</v>
+      </c>
+      <c r="M22">
+        <v>0.001</v>
+      </c>
+      <c r="N22">
+        <v>0.176</v>
+      </c>
+      <c r="O22">
+        <v>0.822</v>
+      </c>
+      <c r="P22">
+        <v>0.0</v>
+      </c>
+      <c r="Q22">
+        <v>2.611</v>
+      </c>
+      <c r="R22">
+        <v>5.456</v>
+      </c>
+      <c r="S22">
+        <v>0.812</v>
+      </c>
+      <c r="T22">
+        <v>1.804</v>
+      </c>
+      <c r="U22">
+        <v>1.079</v>
+      </c>
+      <c r="V22">
+        <v>0.551</v>
+      </c>
+      <c r="W22">
+        <v>0.175</v>
+      </c>
+      <c r="X22">
+        <v>0.088</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="A23">
+        <v>824285</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23">
+        <v>683004</v>
+      </c>
+      <c r="E23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" t="s">
+        <v>99</v>
+      </c>
+      <c r="J23" t="s">
+        <v>98</v>
+      </c>
+      <c r="K23">
+        <v>23.073</v>
+      </c>
+      <c r="L23">
+        <v>5.207</v>
+      </c>
+      <c r="M23">
+        <v>0.19</v>
+      </c>
+      <c r="N23">
+        <v>0.321</v>
+      </c>
+      <c r="O23">
+        <v>0.489</v>
+      </c>
+      <c r="P23">
+        <v>0.329</v>
+      </c>
+      <c r="Q23">
+        <v>12.753</v>
+      </c>
+      <c r="R23">
+        <v>25.374</v>
+      </c>
+      <c r="S23">
+        <v>2.668</v>
+      </c>
+      <c r="T23">
+        <v>4.912</v>
+      </c>
+      <c r="U23">
+        <v>5.099</v>
+      </c>
+      <c r="V23">
+        <v>2.732</v>
+      </c>
+      <c r="W23">
+        <v>0.597</v>
+      </c>
+      <c r="X23">
+        <v>0.317</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24">
+        <v>824364</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24">
+        <v>607536</v>
+      </c>
+      <c r="E24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" t="s">
+        <v>105</v>
+      </c>
+      <c r="J24" t="s">
+        <v>106</v>
+      </c>
+      <c r="K24">
+        <v>23.226</v>
+      </c>
+      <c r="L24">
+        <v>5.304</v>
+      </c>
+      <c r="M24">
+        <v>0.319</v>
+      </c>
+      <c r="N24">
+        <v>0.268</v>
+      </c>
+      <c r="O24">
+        <v>0.413</v>
+      </c>
+      <c r="P24">
+        <v>0.311</v>
+      </c>
+      <c r="Q24">
+        <v>9.099</v>
+      </c>
+      <c r="R24">
+        <v>19.725</v>
+      </c>
+      <c r="S24">
+        <v>3.077</v>
+      </c>
+      <c r="T24">
+        <v>6.258</v>
+      </c>
+      <c r="U24">
+        <v>3.296</v>
+      </c>
+      <c r="V24">
+        <v>1.346</v>
+      </c>
+      <c r="W24">
+        <v>0.83</v>
+      </c>
+      <c r="X24">
+        <v>0.492</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="A25">
+        <v>824364</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25">
+        <v>675911</v>
+      </c>
+      <c r="E25" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" t="s">
+        <v>106</v>
+      </c>
+      <c r="J25" t="s">
+        <v>105</v>
+      </c>
+      <c r="K25">
+        <v>19.555</v>
+      </c>
+      <c r="L25">
+        <v>4.196</v>
+      </c>
+      <c r="M25">
+        <v>0.105</v>
+      </c>
+      <c r="N25">
+        <v>0.344</v>
+      </c>
+      <c r="O25">
+        <v>0.551</v>
+      </c>
+      <c r="P25">
+        <v>0.084</v>
+      </c>
+      <c r="Q25">
+        <v>5.553</v>
+      </c>
+      <c r="R25">
+        <v>13.488</v>
+      </c>
+      <c r="S25">
+        <v>3.235</v>
+      </c>
+      <c r="T25">
+        <v>5.371</v>
+      </c>
+      <c r="U25">
+        <v>3.213</v>
+      </c>
+      <c r="V25">
+        <v>1.736</v>
+      </c>
+      <c r="W25">
+        <v>0.899</v>
+      </c>
+      <c r="X25">
+        <v>0.444</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="A26">
+        <v>824687</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26">
+        <v>518876</v>
+      </c>
+      <c r="E26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" t="s">
+        <v>112</v>
+      </c>
+      <c r="J26" t="s">
+        <v>113</v>
+      </c>
+      <c r="K26">
+        <v>22.007</v>
+      </c>
+      <c r="L26">
+        <v>4.551</v>
+      </c>
+      <c r="M26">
+        <v>0.112</v>
+      </c>
+      <c r="N26">
+        <v>0.408</v>
+      </c>
+      <c r="O26">
+        <v>0.481</v>
+      </c>
+      <c r="P26">
+        <v>0.146</v>
+      </c>
+      <c r="Q26">
+        <v>3.332</v>
+      </c>
+      <c r="R26">
+        <v>11.705</v>
+      </c>
+      <c r="S26">
+        <v>4.02</v>
+      </c>
+      <c r="T26">
+        <v>6.496</v>
+      </c>
+      <c r="U26">
+        <v>2.953</v>
+      </c>
+      <c r="V26">
+        <v>2.205</v>
+      </c>
+      <c r="W26">
+        <v>1.095</v>
+      </c>
+      <c r="X26">
+        <v>0.505</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24">
+      <c r="A27">
+        <v>824687</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27">
+        <v>571510</v>
+      </c>
+      <c r="E27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" t="s">
+        <v>113</v>
+      </c>
+      <c r="J27" t="s">
+        <v>112</v>
+      </c>
+      <c r="K27">
+        <v>21.936</v>
+      </c>
+      <c r="L27">
+        <v>4.805</v>
+      </c>
+      <c r="M27">
+        <v>0.291</v>
+      </c>
+      <c r="N27">
+        <v>0.216</v>
+      </c>
+      <c r="O27">
+        <v>0.493</v>
+      </c>
+      <c r="P27">
+        <v>0.193</v>
+      </c>
+      <c r="Q27">
+        <v>9.484</v>
+      </c>
+      <c r="R27">
+        <v>20.09</v>
+      </c>
+      <c r="S27">
+        <v>3.18</v>
+      </c>
+      <c r="T27">
+        <v>5.859</v>
+      </c>
+      <c r="U27">
+        <v>4.233</v>
+      </c>
+      <c r="V27">
+        <v>1.806</v>
+      </c>
+      <c r="W27">
+        <v>0.852</v>
+      </c>
+      <c r="X27">
+        <v>0.328</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="A28">
+        <v>824769</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28">
+        <v>624133</v>
+      </c>
+      <c r="E28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" t="s">
+        <v>118</v>
+      </c>
+      <c r="J28" t="s">
+        <v>119</v>
+      </c>
+      <c r="K28">
+        <v>23.514</v>
+      </c>
+      <c r="L28">
+        <v>5.331</v>
+      </c>
+      <c r="M28">
+        <v>0.288</v>
+      </c>
+      <c r="N28">
+        <v>0.283</v>
+      </c>
+      <c r="O28">
+        <v>0.429</v>
+      </c>
+      <c r="P28">
+        <v>0.319</v>
+      </c>
+      <c r="Q28">
+        <v>10.329</v>
+      </c>
+      <c r="R28">
+        <v>21.822</v>
+      </c>
+      <c r="S28">
+        <v>2.945</v>
+      </c>
+      <c r="T28">
+        <v>6.311</v>
+      </c>
+      <c r="U28">
+        <v>3.887</v>
+      </c>
+      <c r="V28">
+        <v>1.546</v>
+      </c>
+      <c r="W28">
+        <v>0.651</v>
+      </c>
+      <c r="X28">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="A29">
+        <v>824769</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29">
+        <v>675989</v>
+      </c>
+      <c r="E29" t="s">
+        <v>120</v>
+      </c>
+      <c r="F29" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" t="s">
+        <v>119</v>
+      </c>
+      <c r="J29" t="s">
+        <v>118</v>
+      </c>
+      <c r="K29">
+        <v>8.08</v>
+      </c>
+      <c r="L29">
+        <v>1.685</v>
+      </c>
+      <c r="M29">
+        <v>0.0</v>
+      </c>
+      <c r="N29">
+        <v>0.177</v>
+      </c>
+      <c r="O29">
+        <v>0.823</v>
+      </c>
+      <c r="P29">
+        <v>0.0</v>
+      </c>
+      <c r="Q29">
+        <v>2.435</v>
+      </c>
+      <c r="R29">
+        <v>5.862</v>
+      </c>
+      <c r="S29">
+        <v>1.133</v>
+      </c>
+      <c r="T29">
+        <v>2.139</v>
+      </c>
+      <c r="U29">
+        <v>1.401</v>
+      </c>
+      <c r="V29">
+        <v>1.018</v>
+      </c>
+      <c r="W29">
+        <v>0.181</v>
+      </c>
+      <c r="X29">
+        <v>0.138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="A30">
+        <v>825013</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30">
+        <v>650644</v>
+      </c>
+      <c r="E30" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" t="s">
+        <v>125</v>
+      </c>
+      <c r="J30" t="s">
+        <v>126</v>
+      </c>
+      <c r="K30">
+        <v>22.477</v>
+      </c>
+      <c r="L30">
+        <v>5.295</v>
+      </c>
+      <c r="M30">
+        <v>0.219</v>
+      </c>
+      <c r="N30">
+        <v>0.345</v>
+      </c>
+      <c r="O30">
+        <v>0.436</v>
+      </c>
+      <c r="P30">
+        <v>0.316</v>
+      </c>
+      <c r="Q30">
+        <v>11.11</v>
+      </c>
+      <c r="R30">
+        <v>21.942</v>
+      </c>
+      <c r="S30">
+        <v>2.6</v>
+      </c>
+      <c r="T30">
+        <v>5.288</v>
+      </c>
+      <c r="U30">
+        <v>3.76</v>
+      </c>
+      <c r="V30">
+        <v>1.408</v>
+      </c>
+      <c r="W30">
+        <v>0.882</v>
+      </c>
+      <c r="X30">
+        <v>0.452</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="A31">
+        <v>825013</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31">
         <v>800048</v>
       </c>
-      <c r="E21" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="E31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" t="s">
         <v>38</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H31" t="s">
         <v>34</v>
       </c>
-      <c r="I21" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" t="s">
-        <v>93</v>
-      </c>
-      <c r="K21">
-        <v>22.798</v>
-      </c>
-      <c r="L21">
-        <v>5.47</v>
-      </c>
-      <c r="M21">
-        <v>0.234</v>
-      </c>
-      <c r="N21">
+      <c r="I31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J31" t="s">
+        <v>125</v>
+      </c>
+      <c r="K31">
+        <v>23.304</v>
+      </c>
+      <c r="L31">
+        <v>5.521</v>
+      </c>
+      <c r="M31">
+        <v>0.23</v>
+      </c>
+      <c r="N31">
+        <v>0.258</v>
+      </c>
+      <c r="O31">
+        <v>0.512</v>
+      </c>
+      <c r="P31">
+        <v>0.409</v>
+      </c>
+      <c r="Q31">
+        <v>16.102</v>
+      </c>
+      <c r="R31">
+        <v>29.898</v>
+      </c>
+      <c r="S31">
+        <v>2.427</v>
+      </c>
+      <c r="T31">
+        <v>5.182</v>
+      </c>
+      <c r="U31">
+        <v>5.867</v>
+      </c>
+      <c r="V31">
+        <v>1.697</v>
+      </c>
+      <c r="W31">
+        <v>0.745</v>
+      </c>
+      <c r="X31">
         <v>0.254</v>
-      </c>
-      <c r="O21">
-        <v>0.512</v>
-      </c>
-      <c r="P21">
-        <v>0.406</v>
-      </c>
-      <c r="Q21">
-        <v>16.832</v>
-      </c>
-      <c r="R21">
-        <v>30.675</v>
-      </c>
-      <c r="S21">
-        <v>2.203</v>
-      </c>
-      <c r="T21">
-        <v>4.892</v>
-      </c>
-      <c r="U21">
-        <v>5.95</v>
-      </c>
-      <c r="V21">
-        <v>1.629</v>
-      </c>
-      <c r="W21">
-        <v>0.693</v>
-      </c>
-      <c r="X21">
-        <v>0.222</v>
       </c>
     </row>
   </sheetData>
